--- a/data/trans_bre/P57_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P57_R2-Clase-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 3,32</t>
+          <t>-11,13; 3,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 10,18</t>
+          <t>-2,03; 9,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 10,61</t>
+          <t>-28,29; 9,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 25,3</t>
+          <t>-4,19; 24,67</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,74; -0,31</t>
+          <t>-13,74; -0,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 3,83</t>
+          <t>-9,64; 3,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-40,69; -0,86</t>
+          <t>-38,69; -1,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 8,74</t>
+          <t>-18,83; 7,2</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 3,1</t>
+          <t>-11,67; 4,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-51,76; -7,38</t>
+          <t>-52,8; -6,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-38,97; 11,2</t>
+          <t>-37,97; 17,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-60,11; -15,97</t>
+          <t>-62,7; -14,36</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 6,57</t>
+          <t>-1,67; 6,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-27,27; -0,47</t>
+          <t>-28,23; -0,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 25,41</t>
+          <t>-5,81; 25,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-58,41; -1,16</t>
+          <t>-59,81; -0,93</t>
         </is>
       </c>
     </row>
@@ -841,22 +841,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,5; -1,57</t>
+          <t>-10,47; -1,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,75; -7,07</t>
+          <t>-22,15; -7,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-39,04; -6,95</t>
+          <t>-37,61; -3,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-49,73; -18,97</t>
+          <t>-48,41; -18,41</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-22,59; -10,44</t>
+          <t>-23,95; -10,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,68; -11,84</t>
+          <t>-32,32; -10,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-46,67; -26,14</t>
+          <t>-47,45; -26,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,58; -21,07</t>
+          <t>-44,33; -20,0</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,31; -1,58</t>
+          <t>-6,35; -1,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-25,68; -7,47</t>
+          <t>-26,79; -7,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-20,0; -5,39</t>
+          <t>-19,94; -6,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-43,11; -15,37</t>
+          <t>-44,21; -16,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_R2-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P57_R2-Clase-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,18</t>
+          <t>2,78</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 3,01</t>
+          <t>-11,57; 2,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 9,86</t>
+          <t>-3,51; 8,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 9,69</t>
+          <t>-28,92; 8,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 24,67</t>
+          <t>-7,28; 21,45</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-2,76</t>
+          <t>-3,34</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,79%</t>
+          <t>-6,93%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-13,74; -0,25</t>
+          <t>-13,72; -0,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 3,21</t>
+          <t>-9,62; 2,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,69; -1,15</t>
+          <t>-38,5; -0,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,83; 7,2</t>
+          <t>-18,47; 6,4</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-28,63</t>
+          <t>-8,62</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-42,46%</t>
+          <t>-17,97%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 4,54</t>
+          <t>-12,54; 2,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-52,8; -6,91</t>
+          <t>-15,69; -0,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 17,22</t>
+          <t>-40,05; 11,23</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-62,7; -14,36</t>
+          <t>-31,41; -0,01</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-11,21</t>
+          <t>-2,04</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-24,77%</t>
+          <t>-4,54%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 6,69</t>
+          <t>-1,64; 6,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,23; -0,54</t>
+          <t>-6,09; 3,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 25,43</t>
+          <t>-5,71; 25,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-59,81; -0,93</t>
+          <t>-12,81; 7,29</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-13,8</t>
+          <t>-8,69</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-31,59%</t>
+          <t>-20,78%</t>
         </is>
       </c>
     </row>
@@ -841,29 +841,29 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,47; -1,21</t>
+          <t>-10,71; -1,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,15; -7,48</t>
+          <t>-13,69; -3,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-37,61; -3,59</t>
+          <t>-40,04; -6,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-48,41; -18,41</t>
+          <t>-30,33; -9,55</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-22,1</t>
+          <t>-21,02</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-34,57%</t>
+          <t>-33,18%</t>
         </is>
       </c>
     </row>
@@ -901,22 +901,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,95; -10,46</t>
+          <t>-24,06; -10,48</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,32; -10,84</t>
+          <t>-30,63; -10,02</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,45; -26,0</t>
+          <t>-48,06; -27,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,33; -20,0</t>
+          <t>-42,35; -17,49</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-13,02</t>
+          <t>-5,33</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-25,61%</t>
+          <t>-11,48%</t>
         </is>
       </c>
     </row>
@@ -961,22 +961,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,35; -1,82</t>
+          <t>-6,26; -1,97</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-26,79; -7,83</t>
+          <t>-8,23; -3,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-19,94; -6,11</t>
+          <t>-19,98; -6,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-44,21; -16,19</t>
+          <t>-17,01; -7,18</t>
         </is>
       </c>
     </row>
